--- a/docs/03_要確認事項.xlsx
+++ b/docs/03_要確認事項.xlsx
@@ -867,12 +867,15 @@
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>概要 1.13 の実行ユーザは全 8 件「Administrator」ですが、ローカルの Administrator かドメインの Administrator かが明記されていません。ファイルサーバはドメイン参加サーバのため、どちらも指定しえます。
-現状は vault_task_run_user で指定する実装とし、既定値をAdministrator（ローカル）としています。</t>
+現状は vault_task_run_user で指定する実装とし、既定値をAdministrator（ローカル）としています。
+#### 実機検証の結果（2026-09-17）
+Azure 検証環境（Ansible-TEST-FS / Windows Server 2025 Azure Edition）でplaybooks/03_role_setup.yml を実行したところ、登録対象 7 件すべてが同一の理由で失敗しました。</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>→ PICKLES-CORP\Administrator とすべきかご確認ください。</t>
+          <t>→ PICKLES-CORP\Administrator とすべきかご確認ください。
+→ 本番環境で Administrator が有効かつ SID 解決できることをご確認ください。</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1457,6 +1460,18 @@
       <c r="B10" s="3" t="inlineStr">
         <is>
           <t>仮称で実施：FTP-POD / FTP-NPJS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>B-4 タスク実行ユーザ Administrator</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>今回対象外：実機に当該アカウントが存在せず登録不可。enable_scheduled_tasks: false</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1879,15 @@
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>概要 1.13 の実行ユーザは全 8 件「Administrator」ですが、ローカルの Administrator かドメインの Administrator かが明記されていません。ファイルサーバはドメイン参加サーバのため、どちらも指定しえます。
-現状は vault_task_run_user で指定する実装とし、既定値をAdministrator（ローカル）としています。</t>
+現状は vault_task_run_user で指定する実装とし、既定値をAdministrator（ローカル）としています。
+#### 実機検証の結果（2026-09-17）
+Azure 検証環境（Ansible-TEST-FS / Windows Server 2025 Azure Edition）でplaybooks/03_role_setup.yml を実行したところ、登録対象 7 件すべてが同一の理由で失敗しました。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>→ PICKLES-CORP\Administrator とすべきかご確認ください。</t>
+          <t>→ PICKLES-CORP\Administrator とすべきかご確認ください。
+→ 本番環境で Administrator が有効かつ SID 解決できることをご確認ください。</t>
         </is>
       </c>
     </row>

--- a/docs/03_要確認事項.xlsx
+++ b/docs/03_要確認事項.xlsx
@@ -542,7 +542,7 @@
       <c r="E6" s="3" t="inlineStr">
         <is>
           <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventory/hosts.yml に定義しています。
-【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
+【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS/main.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
         <is>
           <t>概要 1.4 / 1.5 は別紙「【ピックルスコーポレーション様】Azure構成パラメータシート」の「仮想マシン構成情報」を参照、とありますが当該資料が未入手です。
 【今回は仮値で実施】 現状は暫定値として以下を設定しています。
-- inventory/test.yml / inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
+- inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventory/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
 なお、シート8「8.ﾃﾞｨｽｸの管理」の論理容量は C: 126.51GB / System Reserved 500MB /D: 2048GB です。D: は 2TB と大きいため、Azure 側のデータディスク（P40 / E40 / S40 相当以上）の手配が必要です。</t>
         </is>
       </c>
@@ -1549,7 +1549,7 @@
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventory/hosts.yml に定義しています。
-【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
+【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS/main.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <is>
           <t>概要 1.4 / 1.5 は別紙「【ピックルスコーポレーション様】Azure構成パラメータシート」の「仮想マシン構成情報」を参照、とありますが当該資料が未入手です。
 【今回は仮値で実施】 現状は暫定値として以下を設定しています。
-- inventory/test.yml / inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
+- inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventory/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
 なお、シート8「8.ﾃﾞｨｽｸの管理」の論理容量は C: 126.51GB / System Reserved 500MB /D: 2048GB です。D: は 2TB と大きいため、Azure 側のデータディスク（P40 / E40 / S40 相当以上）の手配が必要です。</t>
         </is>
       </c>

--- a/docs/03_要確認事項.xlsx
+++ b/docs/03_要確認事項.xlsx
@@ -645,7 +645,7 @@
         <is>
           <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventory/group_vars/all/main.yml に旧設計書の値を保持しています。
 【今回対象外】 今回の Ansible 初期構築ではドメイン参加を実施しません（enable_domain_join: false）。playbooks/02_domain.yml は現状確認と時刻同期のみ実施します。
-これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
+これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1637,7 +1637,7 @@
         <is>
           <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventory/group_vars/all/main.yml に旧設計書の値を保持しています。
 【今回対象外】 今回の Ansible 初期構築ではドメイン参加を実施しません（enable_domain_join: false）。playbooks/02_domain.yml は現状確認と時刻同期のみ実施します。
-これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
+これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">

--- a/docs/03_要確認事項.xlsx
+++ b/docs/03_要確認事項.xlsx
@@ -541,8 +541,8 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventory/hosts.yml に定義しています。
-【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS/main.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
+          <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventories/pickles/hosts.yml に定義しています。
+【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventories/pickles/test.yml と inventories/pickles/host_vars/Ansible-TEST-FS/main.yml に定義し、実行時は -i inventories/pickles/test.yml で指定します（ansible.cfg に既定のインベントリは置いていません）。</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -576,7 +576,7 @@
         <is>
           <t>概要 1.4 / 1.5 は別紙「【ピックルスコーポレーション様】Azure構成パラメータシート」の「仮想マシン構成情報」を参照、とありますが当該資料が未入手です。
 【今回は仮値で実施】 現状は暫定値として以下を設定しています。
-- inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventory/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
+- inventories/pickles/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventories/pickles/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
 なお、シート8「8.ﾃﾞｨｽｸの管理」の論理容量は C: 126.51GB / System Reserved 500MB /D: 2048GB です。D: は 2TB と大きいため、Azure 側のデータディスク（P40 / E40 / S40 相当以上）の手配が必要です。</t>
         </is>
       </c>
@@ -609,7 +609,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>【今回は仮値で実施】 inventory/group_vars/all/vault.yml に仮パスワード（P@ssw0rd-Change-Me-NN）を設定済みです。本ファイルは .gitignore によりリポジトリ管理外です。
+          <t>【今回は仮値で実施】 inventories/pickles/group_vars/all/vault.yml に仮パスワード（P@ssw0rd-Change-Me-NN）を設定済みです。本ファイルは .gitignore によりリポジトリ管理外です。
 なお、概要 1.3 の列見出しではファイルサーバのローカルユーザは Administrator です。vault_local_admin_user の既定は旧設計書由来の picklesadmin のままとしています。</t>
         </is>
       </c>
@@ -643,9 +643,9 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventory/group_vars/all/main.yml に旧設計書の値を保持しています。
+          <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventories/pickles/group_vars/all/main.yml に旧設計書の値を保持しています。
 【今回対象外】 今回の Ansible 初期構築ではドメイン参加を実施しません（enable_domain_join: false）。playbooks/02_domain.yml は現状確認と時刻同期のみ実施します。
-これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
+これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventories/pickles/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -678,7 +678,7 @@
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>概要 1.13 No.1 のスケジュールが 「指定日時 2025/02/07 18:25に起動」 です。現行環境の設定をそのまま転記した値と思われますが、この日時は既に過ぎているため、新環境に同じ設定で登録してもタスクは起動しません。
-【今回対象外】 当該タスクは登録しません。inventory/group_vars/fileserver.yml の該当エントリに skip: true を設定しており、win_tasks ロールが登録対象から除外し、実行ログに【今回対象外】SHM商品マスター更新 : ... と出力します。残り 7 件のタスクは設計書どおり登録します。</t>
+【今回対象外】 当該タスクは登録しません。inventories/pickles/group_vars/fileserver.yml の該当エントリに skip: true を設定しており、win_tasks ロールが登録対象から除外し、実行ログに【今回対象外】SHM商品マスター更新 : ... と出力します。残り 7 件のタスクは設計書どおり登録します。</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>概要シートの記載を採用し、inventory/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
+          <t>概要シートの記載を採用し、inventories/pickles/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -713,7 +713,7 @@
           <t>シート8「6.ﾛｰｶﾙﾕｰｻﾞｰ」に記載があるのは OS 組み込みのDefaultAccount / Guest / WDAGUtilityAccount のみで、それ以外の行（181/184/185 行）はユーザ名がマスクされています。「7.ﾛｰｶﾙｸﾞﾙｰﾌﾟ」の所属ユーザ欄も同様にマスクされています（Administrators = 「-」、Remote Desktop Users = 「-」など）。
 一方、概要シートには以下の記載があります。
 - 1.3 No.7 : ローカルユーザ Administrator ／ その他 kansai（Remote Desktop Users、Users グループに所属）- 1.16 : FTP 認証ユーザ docways / NPJS
-現状の実装: 概要シートの記載を採用し、inventory/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
+現状の実装: 概要シートの記載を採用し、inventories/pickles/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -740,13 +740,13 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventory/group_vars/fileserver.yml の ftp_sites[].name）。</t>
+          <t>IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventories/pickles/group_vars/fileserver.yml の ftp_sites[].name）。</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>概要 1.16 の「サイト名」欄（F 列）がマスクされています。前版の設計書では No.1「FAX送信用」／ No.2「NPJS」 でした。
-現状の実装: IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventory/group_vars/fileserver.yml の ftp_sites[].name）。
+現状の実装: IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventories/pickles/group_vars/fileserver.yml の ftp_sites[].name）。
 サイト名は IIS の管理単位であり、現行環境と名前を揃えないと運用手順書やスクリプトと食い違う可能性があります。</t>
         </is>
       </c>
@@ -1081,7 +1081,7 @@
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>概要 1.6「日本語を使用する」に対し、Azure Marketplace の日本語イメージを使用する前提でinstall_ja_language_pack: false としています。英語イメージから構築する場合はinventory/group_vars/all/main.yml で true に変更してください（言語パックのダウンロードにインターネット接続が必要です）。</t>
+          <t>概要 1.6「日本語を使用する」に対し、Azure Marketplace の日本語イメージを使用する前提でinstall_ja_language_pack: false としています。英語イメージから構築する場合はinventories/pickles/group_vars/all/main.yml で true に変更してください（言語パックのダウンロードにインターネット接続が必要です）。</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>仮値で実施：検証機を Ansible-TEST-FS として inventory/test.yml に定義</t>
+          <t>仮値で実施：検証機を Ansible-TEST-FS として inventories/pickles/test.yml に定義</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>仮値で実施：inventory/group_vars/all/vault.yml に仮パスワードを設定済み</t>
+          <t>仮値で実施：inventories/pickles/group_vars/all/vault.yml に仮パスワードを設定済み</t>
         </is>
       </c>
     </row>
@@ -1548,8 +1548,8 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventory/hosts.yml に定義しています。
-【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventory/test.yml と inventory/host_vars/Ansible-TEST-FS/main.yml に定義し、ansible.cfg の既定インベントリを inventory/test.yml に設定しています。</t>
+          <t>概要シートの各表の「ホスト名」欄（F 列）が空欄、シート8「3.ｻｰﾊﾞｰ ﾏﾈｰｼﾞｬｰ &gt; ﾛｰｶﾙ ｻｰﾊﾞｰ」の「ｺﾝﾋﾟｭｰﾀ名」も空欄です。本文中の記述から以下のとおり採番して inventories/pickles/hosts.yml に定義しています。
+【今回は仮値で実施】 検証機のホスト名を Ansible-TEST-FS としています。inventories/pickles/test.yml と inventories/pickles/host_vars/Ansible-TEST-FS/main.yml に定義し、実行時は -i inventories/pickles/test.yml で指定します（ansible.cfg に既定のインベントリは置いていません）。</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <is>
           <t>概要 1.4 / 1.5 は別紙「【ピックルスコーポレーション様】Azure構成パラメータシート」の「仮想マシン構成情報」を参照、とありますが当該資料が未入手です。
 【今回は仮値で実施】 現状は暫定値として以下を設定しています。
-- inventory/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventory/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
+- inventories/pickles/hosts.yml の ansible_host : 10.0.1.11〜10.0.1.17（仮値）検証機の接続先は inventories/pickles/host_vars/Ansible-TEST-FS/connection.yml（git 管理外）- データディスク : disk_number: 2 / D: / MBR / NTFS / ラベル「ボリューム」
 なお、シート8「8.ﾃﾞｨｽｸの管理」の論理容量は C: 126.51GB / System Reserved 500MB /D: 2048GB です。D: は 2TB と大きいため、Azure 側のデータディスク（P40 / E40 / S40 相当以上）の手配が必要です。</t>
         </is>
       </c>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>【今回は仮値で実施】 inventory/group_vars/all/vault.yml に仮パスワード（P@ssw0rd-Change-Me-NN）を設定済みです。本ファイルは .gitignore によりリポジトリ管理外です。
+          <t>【今回は仮値で実施】 inventories/pickles/group_vars/all/vault.yml に仮パスワード（P@ssw0rd-Change-Me-NN）を設定済みです。本ファイルは .gitignore によりリポジトリ管理外です。
 なお、概要 1.3 の列見出しではファイルサーバのローカルユーザは Administrator です。vault_local_admin_user の既定は旧設計書由来の picklesadmin のままとしています。</t>
         </is>
       </c>
@@ -1635,9 +1635,9 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventory/group_vars/all/main.yml に旧設計書の値を保持しています。
+          <t>概要 1.2 は「7 台すべてドメインに参加する」となっており、ファイルサーバも メンバーサーバとして参加します（DC 昇格はしません）。旧設計書 1.2 にあった「PICKLES-CORP.pickles.co.jp に参加する（※現行踏襲）」の本文はサンプル版ではマスクされていますが、ドメイン名はinventories/pickles/group_vars/all/main.yml に旧設計書の値を保持しています。
 【今回対象外】 今回の Ansible 初期構築ではドメイン参加を実施しません（enable_domain_join: false）。playbooks/02_domain.yml は現状確認と時刻同期のみ実施します。
-これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventory/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
+これに伴い、検証機は時刻同期先が無くなるため、検証機に限り外部 NTP（ntp.nict.jp,0x8）と手動同期させています（inventories/pickles/host_vars/Ansible-TEST-FS/main.yml の is_pdc_emulator: true）。ドメイン参加を有効化する際は false に戻してください（概要 1.8 のとおり自動同期になります）。</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1665,7 +1665,7 @@
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>概要 1.13 No.1 のスケジュールが 「指定日時 2025/02/07 18:25に起動」 です。現行環境の設定をそのまま転記した値と思われますが、この日時は既に過ぎているため、新環境に同じ設定で登録してもタスクは起動しません。
-【今回対象外】 当該タスクは登録しません。inventory/group_vars/fileserver.yml の該当エントリに skip: true を設定しており、win_tasks ロールが登録対象から除外し、実行ログに【今回対象外】SHM商品マスター更新 : ... と出力します。残り 7 件のタスクは設計書どおり登録します。</t>
+【今回対象外】 当該タスクは登録しません。inventories/pickles/group_vars/fileserver.yml の該当エントリに skip: true を設定しており、win_tasks ロールが登録対象から除外し、実行ログに【今回対象外】SHM商品マスター更新 : ... と出力します。残り 7 件のタスクは設計書どおり登録します。</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>概要シートの記載を採用し、inventory/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
+          <t>概要シートの記載を採用し、inventories/pickles/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1695,7 +1695,7 @@
           <t>シート8「6.ﾛｰｶﾙﾕｰｻﾞｰ」に記載があるのは OS 組み込みのDefaultAccount / Guest / WDAGUtilityAccount のみで、それ以外の行（181/184/185 行）はユーザ名がマスクされています。「7.ﾛｰｶﾙｸﾞﾙｰﾌﾟ」の所属ユーザ欄も同様にマスクされています（Administrators = 「-」、Remote Desktop Users = 「-」など）。
 一方、概要シートには以下の記載があります。
 - 1.3 No.7 : ローカルユーザ Administrator ／ その他 kansai（Remote Desktop Users、Users グループに所属）- 1.16 : FTP 認証ユーザ docways / NPJS
-現状の実装: 概要シートの記載を採用し、inventory/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
+現状の実装: 概要シートの記載を採用し、inventories/pickles/group_vars/fileserver.yml のlocal_users に kansai / docways / NPJS の 3 ユーザを定義しています。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1717,13 +1717,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventory/group_vars/fileserver.yml の ftp_sites[].name）。</t>
+          <t>IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventories/pickles/group_vars/fileserver.yml の ftp_sites[].name）。</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>概要 1.16 の「サイト名」欄（F 列）がマスクされています。前版の設計書では No.1「FAX送信用」／ No.2「NPJS」 でした。
-現状の実装: IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventory/group_vars/fileserver.yml の ftp_sites[].name）。
+現状の実装: IIS 上のサイト名として仮称 FTP-POD / FTP-NPJS を設定しています（inventories/pickles/group_vars/fileserver.yml の ftp_sites[].name）。
 サイト名は IIS の管理単位であり、現行環境と名前を揃えないと運用手順書やスクリプトと食い違う可能性があります。</t>
         </is>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>概要 1.6「日本語を使用する」に対し、Azure Marketplace の日本語イメージを使用する前提でinstall_ja_language_pack: false としています。英語イメージから構築する場合はinventory/group_vars/all/main.yml で true に変更してください（言語パックのダウンロードにインターネット接続が必要です）。</t>
+          <t>概要 1.6「日本語を使用する」に対し、Azure Marketplace の日本語イメージを使用する前提でinstall_ja_language_pack: false としています。英語イメージから構築する場合はinventories/pickles/group_vars/all/main.yml で true に変更してください（言語パックのダウンロードにインターネット接続が必要です）。</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
